--- a/Notebooks/FRB_Surajit.xlsx
+++ b/Notebooks/FRB_Surajit.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_GW_association_cosmo\Notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C422C16-7A62-4CE6-AD1B-110843DD81C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA96D15-A005-4B39-8F93-8BB249741B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{5C9607F5-72C0-4E57-83BF-8A0CBC4332AB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5C9607F5-72C0-4E57-83BF-8A0CBC4332AB}"/>
   </bookViews>
   <sheets>
     <sheet name="FRB_Surajit" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -243,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +403,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -843,9 +851,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1202,12 +1208,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6C6722-8B48-4B34-B58C-77350BB8C300}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.625" customWidth="1"/>
+    <col min="1" max="1" width="19.58203125" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +1237,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1251,7 +1258,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1272,7 +1279,7 @@
         <v>76.099999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1293,7 +1300,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1314,7 +1321,7 @@
         <v>149.30000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1335,7 +1342,7 @@
         <v>320.92</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1356,7 +1363,7 @@
         <v>487.27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1377,7 +1384,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1398,7 +1405,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1419,7 +1426,7 @@
         <v>306.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1447,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1461,7 +1468,7 @@
         <v>193.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1482,7 +1489,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1503,7 +1510,7 @@
         <v>79.199999999999989</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1524,7 +1531,7 @@
         <v>1091.7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1545,7 +1552,7 @@
         <v>723.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1566,7 +1573,7 @@
         <v>301.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1587,7 +1594,7 @@
         <v>263.57</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1608,7 +1615,7 @@
         <v>875.7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1629,7 +1636,7 @@
         <v>536.70000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1650,7 +1657,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1671,7 +1678,7 @@
         <v>462.22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1692,7 +1699,7 @@
         <v>307.2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1713,7 +1720,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1734,7 +1741,7 @@
         <v>156.20000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1755,7 +1762,7 @@
         <v>353.1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1776,7 +1783,7 @@
         <v>541.79999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1797,7 +1804,7 @@
         <v>181.62</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1818,7 +1825,7 @@
         <v>290.32</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1839,7 +1846,7 @@
         <v>695.6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1860,7 +1867,7 @@
         <v>342.8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1881,7 +1888,7 @@
         <v>49.069999999999936</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1902,7 +1909,7 @@
         <v>522.57999999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1923,7 +1930,7 @@
         <v>460.14699999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1944,7 +1951,7 @@
         <v>130.69999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1965,7 +1972,7 @@
         <v>192.33</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1986,7 +1993,7 @@
         <v>573.20000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2007,7 +2014,7 @@
         <v>178.9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -2028,7 +2035,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
@@ -2048,12 +2055,12 @@
         <f t="shared" si="0"/>
         <v>183.07999999999998</v>
       </c>
-      <c r="G40" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="G40" s="3">
+        <v>182.98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>69</v>
       </c>
       <c r="B41">
@@ -2074,7 +2081,7 @@
       </c>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -2094,11 +2101,11 @@
         <f t="shared" si="0"/>
         <v>416.84000000000003</v>
       </c>
-      <c r="G42" s="2">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G42" s="3">
+        <v>416.71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -2118,12 +2125,12 @@
         <f t="shared" si="0"/>
         <v>45.7</v>
       </c>
-      <c r="G43" s="2">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="G43" s="3">
+        <v>-22.31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B44">
@@ -2142,8 +2149,11 @@
         <f t="shared" si="0"/>
         <v>585.65</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G44" s="3">
+        <v>585.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -2164,7 +2174,7 @@
         <v>418.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -2184,11 +2194,11 @@
         <f t="shared" si="0"/>
         <v>307.87</v>
       </c>
-      <c r="G46" s="2">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G46" s="3">
+        <v>307.81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,11 +2218,11 @@
         <f t="shared" si="0"/>
         <v>214.32999999999998</v>
       </c>
-      <c r="G47" s="2">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G47" s="3">
+        <v>214.29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -2233,7 +2243,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -2254,7 +2264,7 @@
         <v>259.39999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -2274,11 +2284,11 @@
         <f t="shared" si="0"/>
         <v>571.54</v>
       </c>
-      <c r="G50" s="2">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G50" s="3">
+        <v>571.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -2299,7 +2309,7 @@
         <v>94.460000000000008</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -2319,11 +2329,11 @@
         <f t="shared" si="0"/>
         <v>576.07999999999993</v>
       </c>
-      <c r="G52" s="2">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G52" s="3">
+        <v>575.86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -2344,7 +2354,7 @@
         <v>615.79999999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -2364,11 +2374,11 @@
         <f t="shared" si="0"/>
         <v>274.69</v>
       </c>
-      <c r="G54" s="2">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G54" s="3">
+        <v>274.68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -2388,11 +2398,11 @@
         <f t="shared" si="0"/>
         <v>386.68</v>
       </c>
-      <c r="G55" s="2">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G55" s="3">
+        <v>387.85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -2413,7 +2423,7 @@
         <v>308.8</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -2434,7 +2444,7 @@
         <v>311.39999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -2455,7 +2465,7 @@
         <v>361.51</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -2476,7 +2486,7 @@
         <v>83.600000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -2497,7 +2507,7 @@
         <v>406.1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -2518,7 +2528,7 @@
         <v>184.89999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -2539,7 +2549,7 @@
         <v>487.70000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -2560,7 +2570,7 @@
         <v>336.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -2581,7 +2591,7 @@
         <v>252.73000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
